--- a/游戏设计王/老虎机数学专题-马可夫链.xlsx
+++ b/游戏设计王/老虎机数学专题-马可夫链.xlsx
@@ -1109,7 +1109,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1191,6 +1191,8 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" applyNumberFormat="1" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" applyNumberFormat="1" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4998,7 +5000,7 @@
       <c r="A8" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="39">
         <f>SUM(B5:B7)</f>
         <v>1</v>
       </c>
@@ -5008,43 +5010,43 @@
       <c r="D8" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="39">
         <f t="shared" ref="E8:N8" si="3">SUM(E5:E7)</f>
         <v>1</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="39">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="39">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="39">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="39">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="39">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="39">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="39">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="39">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="39">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
